--- a/WasteGrab_Feature_QA_Tracker.xlsx
+++ b/WasteGrab_Feature_QA_Tracker.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="Re7f92116730c4e71"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feature Tracker" sheetId="2" r:id="R884d9fba3b3945e2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bug Tracker" sheetId="3" r:id="R0fa1b1fe4b7747ac"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Cases" sheetId="4" r:id="Rf22087c42d1c4ee8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="5" r:id="Ra6f9bb87f3a44ef3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R97a8d8eeaceb48d4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feature Tracker" sheetId="2" r:id="Raab098173d4c4da4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bug Tracker" sheetId="3" r:id="R1ead98da03c14d81"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Cases" sheetId="4" r:id="R32e009ac63054a20"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="5" r:id="R2dd13f5e3e424792"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -74,7 +74,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="55">
+  <x:cellXfs count="58">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -196,6 +196,13 @@
     <x:xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -206,7 +213,7 @@
         <x:color rgb="166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="DCFCE7"/>
         </x:patternFill>
       </x:fill>
@@ -216,7 +223,7 @@
         <x:color rgb="166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="DCFCE7"/>
         </x:patternFill>
       </x:fill>
@@ -226,7 +233,7 @@
         <x:color rgb="166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="DCFCE7"/>
         </x:patternFill>
       </x:fill>
@@ -236,7 +243,7 @@
         <x:color rgb="991B1B"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FEE2E2"/>
         </x:patternFill>
       </x:fill>
@@ -246,7 +253,7 @@
         <x:color rgb="92400E"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FEF3C7"/>
         </x:patternFill>
       </x:fill>
@@ -256,7 +263,7 @@
         <x:color rgb="1E40AF"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="DBEAFE"/>
         </x:patternFill>
       </x:fill>
@@ -266,7 +273,7 @@
         <x:color rgb="991B1B"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FEE2E2"/>
         </x:patternFill>
       </x:fill>
@@ -276,7 +283,7 @@
         <x:color rgb="1E40AF"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="DBEAFE"/>
         </x:patternFill>
       </x:fill>
@@ -286,7 +293,7 @@
         <x:color rgb="166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="DCFCE7"/>
         </x:patternFill>
       </x:fill>
@@ -296,7 +303,7 @@
         <x:color rgb="166534"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="DCFCE7"/>
         </x:patternFill>
       </x:fill>
@@ -306,7 +313,7 @@
         <x:color rgb="991B1B"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FEE2E2"/>
         </x:patternFill>
       </x:fill>
@@ -316,7 +323,7 @@
         <x:color rgb="92400E"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FEF3C7"/>
         </x:patternFill>
       </x:fill>
@@ -466,7 +473,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R78c69bbbfd2845d7"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R56d6906c1c564045"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -742,7 +749,7 @@
       </x:c>
       <x:c r="B4" s="22" t="n">
         <x:f>COUNTA('Feature Tracker'!A2:A200)</x:f>
-        <x:v>60</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C4" s="22"/>
       <x:c r="D4" s="22"/>
@@ -818,7 +825,7 @@
       </x:c>
       <x:c r="B8" s="22" t="n">
         <x:f>COUNTIF('Feature Tracker'!G2:G200,"Needs Review")</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C8" s="22"/>
       <x:c r="D8" s="22"/>
@@ -836,8 +843,8 @@
         <x:v>Open Bugs</x:v>
       </x:c>
       <x:c r="B9" s="22" t="n">
-        <x:f>COUNTIF('Bug Tracker'!E2:E200,"Open")+COUNTIF('Bug Tracker'!E2:E200,"In Progress")</x:f>
-        <x:v>5</x:v>
+        <x:f>COUNTIFS('Bug Tracker'!E2:E200,"Open",'Bug Tracker'!F2:F200,"&lt;&gt;")</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C9" s="22"/>
       <x:c r="D9" s="22"/>
@@ -900,12 +907,12 @@
         <x:v>Not Tested</x:v>
       </x:c>
       <x:c r="B13" s="22" t="n">
-        <x:f>COUNTIF('Feature Tracker'!G2:G200,"Not Tested")</x:f>
-        <x:v>60</x:v>
+        <x:f>COUNTIF('Feature Tracker'!G2:G200,A13)</x:f>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C13" s="25" t="n">
         <x:f>IF($B$4=0,0,B13/$B$4)</x:f>
-        <x:v>1</x:v>
+        <x:v>0.9864864864864865</x:v>
       </x:c>
       <x:c r="D13" s="22"/>
       <x:c r="E13" s="22"/>
@@ -918,7 +925,7 @@
         <x:v>In Progress</x:v>
       </x:c>
       <x:c r="B14" s="22" t="n">
-        <x:f>COUNTIF('Feature Tracker'!G2:G200,"In Progress")</x:f>
+        <x:f>COUNTIF('Feature Tracker'!G2:G200,A14)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="C14" s="25" t="n">
@@ -936,7 +943,7 @@
         <x:v>Passed</x:v>
       </x:c>
       <x:c r="B15" s="22" t="n">
-        <x:f>COUNTIF('Feature Tracker'!G2:G200,"Passed")</x:f>
+        <x:f>COUNTIF('Feature Tracker'!G2:G200,A15)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="C15" s="25" t="n">
@@ -954,7 +961,7 @@
         <x:v>Failed</x:v>
       </x:c>
       <x:c r="B16" s="22" t="n">
-        <x:f>COUNTIF('Feature Tracker'!G2:G200,"Failed")</x:f>
+        <x:f>COUNTIF('Feature Tracker'!G2:G200,A16)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="C16" s="25" t="n">
@@ -972,7 +979,7 @@
         <x:v>Blocked</x:v>
       </x:c>
       <x:c r="B17" s="22" t="n">
-        <x:f>COUNTIF('Feature Tracker'!G2:G200,"Blocked")</x:f>
+        <x:f>COUNTIF('Feature Tracker'!G2:G200,A17)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="C17" s="25" t="n">
@@ -990,12 +997,12 @@
         <x:v>Needs Review</x:v>
       </x:c>
       <x:c r="B18" s="22" t="n">
-        <x:f>COUNTIF('Feature Tracker'!G2:G200,"Needs Review")</x:f>
-        <x:v>0</x:v>
+        <x:f>COUNTIF('Feature Tracker'!G2:G200,A18)</x:f>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C18" s="25" t="n">
         <x:f>IF($B$4=0,0,B18/$B$4)</x:f>
-        <x:v>0</x:v>
+        <x:v>0.013513513513513514</x:v>
       </x:c>
       <x:c r="D18" s="22"/>
       <x:c r="E18" s="22"/>
@@ -1029,7 +1036,7 @@
     <x:mergeCell ref="E3:H3"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R23afca039d3e4410"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb301b23c394a4da6"/>
 </x:worksheet>
 </file>
 
@@ -1037,20 +1044,20 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="12" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="20" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="16" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="11.039999961853027" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="14.9399995803833" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="17.770000457763672" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="30" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="45" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="34" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="10" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="12" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="16" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="14" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="14" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="38" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="24" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="30" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="30" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="13.319999694824219" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="7.539999961853027" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="8.880000114440918" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="8.210000038146973" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="11.569999694824219" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="7.940000057220459" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="30" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="30" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -1578,19 +1585,19 @@
         <x:v>WG-F015</x:v>
       </x:c>
       <x:c r="B16" s="22" t="str">
-        <x:v>Auth</x:v>
+        <x:v>Auth / Onboarding</x:v>
       </x:c>
       <x:c r="C16" s="22" t="str">
-        <x:v>Customer</x:v>
+        <x:v>All</x:v>
       </x:c>
       <x:c r="D16" s="22" t="str">
-        <x:v>Customer onboarding completion</x:v>
+        <x:v>Role onboarding completion</x:v>
       </x:c>
       <x:c r="E16" s="22" t="str">
-        <x:v>Customer onboarding status can be completed and reflected in UI</x:v>
+        <x:v>Customer, collector, and admin onboarding completion states render and persist correctly</x:v>
       </x:c>
       <x:c r="F16" s="22" t="str">
-        <x:v>/api/auth/onboarding</x:v>
+        <x:v>/api/auth/onboarding + role onboarding pages</x:v>
       </x:c>
       <x:c r="G16" s="22" t="str">
         <x:v>Not Tested</x:v>
@@ -1599,13 +1606,15 @@
         <x:v>☐</x:v>
       </x:c>
       <x:c r="I16" s="22" t="str">
-        <x:v>Medium</x:v>
-      </x:c>
-      <x:c r="J16" s="22" t="str"/>
-      <x:c r="K16" s="52" t="str"/>
-      <x:c r="L16" s="22" t="str"/>
-      <x:c r="M16" s="22" t="str"/>
-      <x:c r="N16" s="22" t="str"/>
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="J16" s="22"/>
+      <x:c r="K16" s="52"/>
+      <x:c r="L16" s="22"/>
+      <x:c r="M16" s="22" t="str">
+        <x:v>Expanded from customer-only onboarding to all roles</x:v>
+      </x:c>
+      <x:c r="N16" s="22"/>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="22" t="str">
@@ -1686,13 +1695,13 @@
         <x:v>Collector</x:v>
       </x:c>
       <x:c r="D19" s="22" t="str">
-        <x:v>Collector pickup access</x:v>
+        <x:v>Collector pickup access scopes</x:v>
       </x:c>
       <x:c r="E19" s="22" t="str">
-        <x:v>Collector can access assigned/available pickup data only</x:v>
+        <x:v>Collector can access available pickups and own accepted pickups only; unrelated protected data is blocked</x:v>
       </x:c>
       <x:c r="F19" s="22" t="str">
-        <x:v>/api/collector or collector pages</x:v>
+        <x:v>Collector available/my pickup pages + APIs</x:v>
       </x:c>
       <x:c r="G19" s="22" t="str">
         <x:v>Not Tested</x:v>
@@ -1703,11 +1712,13 @@
       <x:c r="I19" s="22" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="J19" s="22" t="str"/>
-      <x:c r="K19" s="52" t="str"/>
-      <x:c r="L19" s="22" t="str"/>
-      <x:c r="M19" s="22" t="str"/>
-      <x:c r="N19" s="22" t="str"/>
+      <x:c r="J19" s="22"/>
+      <x:c r="K19" s="52"/>
+      <x:c r="L19" s="22"/>
+      <x:c r="M19" s="22" t="str">
+        <x:v>Split available vs my pickups in testing</x:v>
+      </x:c>
+      <x:c r="N19" s="22"/>
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="22" t="str">
@@ -2397,16 +2408,16 @@
         <x:v>Pickup Lifecycle</x:v>
       </x:c>
       <x:c r="C40" s="22" t="str">
-        <x:v>Collector/Admin</x:v>
+        <x:v>Collector</x:v>
       </x:c>
       <x:c r="D40" s="22" t="str">
-        <x:v>Pending to Accepted</x:v>
+        <x:v>Accept pending pickup</x:v>
       </x:c>
       <x:c r="E40" s="22" t="str">
-        <x:v>Collector/admin can move pickup from PENDING to ACCEPTED</x:v>
+        <x:v>Collector can move pickup from PENDING to ACCEPTED through the collector workflow</x:v>
       </x:c>
       <x:c r="F40" s="22" t="str">
-        <x:v>PickupStatus ACCEPTED</x:v>
+        <x:v>Collector action workflow / PickupStatus ACCEPTED</x:v>
       </x:c>
       <x:c r="G40" s="22" t="str">
         <x:v>Not Tested</x:v>
@@ -2417,11 +2428,13 @@
       <x:c r="I40" s="22" t="str">
         <x:v>Critical</x:v>
       </x:c>
-      <x:c r="J40" s="22" t="str"/>
-      <x:c r="K40" s="52" t="str"/>
-      <x:c r="L40" s="22" t="str"/>
-      <x:c r="M40" s="22" t="str"/>
-      <x:c r="N40" s="22" t="str"/>
+      <x:c r="J40" s="22"/>
+      <x:c r="K40" s="52"/>
+      <x:c r="L40" s="22"/>
+      <x:c r="M40" s="22" t="str">
+        <x:v>Admin list/view only unless assign endpoint is reintroduced</x:v>
+      </x:c>
+      <x:c r="N40" s="22"/>
     </x:row>
     <x:row r="41">
       <x:c r="A41" s="22" t="str">
@@ -2431,16 +2444,16 @@
         <x:v>Pickup Lifecycle</x:v>
       </x:c>
       <x:c r="C41" s="22" t="str">
-        <x:v>Collector/Admin</x:v>
+        <x:v>Collector</x:v>
       </x:c>
       <x:c r="D41" s="22" t="str">
-        <x:v>Accepted to Arrived</x:v>
+        <x:v>Mark pickup arrived</x:v>
       </x:c>
       <x:c r="E41" s="22" t="str">
-        <x:v>Collector/admin can mark pickup as ARRIVED</x:v>
+        <x:v>Collector can mark an accepted pickup as ARRIVED</x:v>
       </x:c>
       <x:c r="F41" s="22" t="str">
-        <x:v>PickupStatus ARRIVED</x:v>
+        <x:v>Collector action workflow / PickupStatus ARRIVED</x:v>
       </x:c>
       <x:c r="G41" s="22" t="str">
         <x:v>Not Tested</x:v>
@@ -2451,11 +2464,13 @@
       <x:c r="I41" s="22" t="str">
         <x:v>High</x:v>
       </x:c>
-      <x:c r="J41" s="22" t="str"/>
-      <x:c r="K41" s="52" t="str"/>
-      <x:c r="L41" s="22" t="str"/>
-      <x:c r="M41" s="22" t="str"/>
-      <x:c r="N41" s="22" t="str"/>
+      <x:c r="J41" s="22"/>
+      <x:c r="K41" s="52"/>
+      <x:c r="L41" s="22"/>
+      <x:c r="M41" s="22" t="str">
+        <x:v>Collector-side lifecycle action</x:v>
+      </x:c>
+      <x:c r="N41" s="22"/>
     </x:row>
     <x:row r="42">
       <x:c r="A42" s="22" t="str">
@@ -2465,16 +2480,16 @@
         <x:v>Pickup Lifecycle</x:v>
       </x:c>
       <x:c r="C42" s="22" t="str">
-        <x:v>Collector/Admin</x:v>
+        <x:v>Collector</x:v>
       </x:c>
       <x:c r="D42" s="22" t="str">
-        <x:v>Arrived to Verified</x:v>
+        <x:v>Verify pickup values</x:v>
       </x:c>
       <x:c r="E42" s="22" t="str">
-        <x:v>Actual weight/category verification saves correctly</x:v>
+        <x:v>Collector can save actual weight/category values and move pickup to VERIFIED</x:v>
       </x:c>
       <x:c r="F42" s="22" t="str">
-        <x:v>PickupStatus VERIFIED</x:v>
+        <x:v>Collector verification workflow / PickupStatus VERIFIED</x:v>
       </x:c>
       <x:c r="G42" s="22" t="str">
         <x:v>Not Tested</x:v>
@@ -2485,11 +2500,13 @@
       <x:c r="I42" s="22" t="str">
         <x:v>Critical</x:v>
       </x:c>
-      <x:c r="J42" s="22" t="str"/>
-      <x:c r="K42" s="52" t="str"/>
-      <x:c r="L42" s="22" t="str"/>
-      <x:c r="M42" s="22" t="str"/>
-      <x:c r="N42" s="22" t="str"/>
+      <x:c r="J42" s="22"/>
+      <x:c r="K42" s="52"/>
+      <x:c r="L42" s="22"/>
+      <x:c r="M42" s="22" t="str">
+        <x:v>Must compare customer/AI estimate vs collector verified values</x:v>
+      </x:c>
+      <x:c r="N42" s="22"/>
     </x:row>
     <x:row r="43">
       <x:c r="A43" s="22" t="str">
@@ -2499,16 +2516,16 @@
         <x:v>Pickup Lifecycle</x:v>
       </x:c>
       <x:c r="C43" s="22" t="str">
-        <x:v>Collector/Admin</x:v>
+        <x:v>Collector</x:v>
       </x:c>
       <x:c r="D43" s="22" t="str">
-        <x:v>Verified to Completed</x:v>
+        <x:v>Complete verified pickup</x:v>
       </x:c>
       <x:c r="E43" s="22" t="str">
-        <x:v>Completed pickup finalizes and triggers points where expected</x:v>
+        <x:v>Collector can complete a verified pickup and points are awarded where expected</x:v>
       </x:c>
       <x:c r="F43" s="22" t="str">
-        <x:v>PickupStatus COMPLETED</x:v>
+        <x:v>Collector action workflow / PickupStatus COMPLETED</x:v>
       </x:c>
       <x:c r="G43" s="22" t="str">
         <x:v>Not Tested</x:v>
@@ -2519,11 +2536,13 @@
       <x:c r="I43" s="22" t="str">
         <x:v>Critical</x:v>
       </x:c>
-      <x:c r="J43" s="22" t="str"/>
-      <x:c r="K43" s="52" t="str"/>
-      <x:c r="L43" s="22" t="str"/>
-      <x:c r="M43" s="22" t="str"/>
-      <x:c r="N43" s="22" t="str"/>
+      <x:c r="J43" s="22"/>
+      <x:c r="K43" s="52"/>
+      <x:c r="L43" s="22"/>
+      <x:c r="M43" s="22" t="str">
+        <x:v>Collector-side lifecycle action</x:v>
+      </x:c>
+      <x:c r="N43" s="22"/>
     </x:row>
     <x:row r="44">
       <x:c r="A44" s="22" t="str">
@@ -2570,28 +2589,30 @@
         <x:v>Admin</x:v>
       </x:c>
       <x:c r="D45" s="22" t="str">
-        <x:v>Assign collector</x:v>
+        <x:v>Admin pickup list/detail only</x:v>
       </x:c>
       <x:c r="E45" s="22" t="str">
-        <x:v>Admin can assign or update collector for a pickup</x:v>
+        <x:v>Admin can list and view pickup details; collector assignment endpoint is not currently confirmed</x:v>
       </x:c>
       <x:c r="F45" s="22" t="str">
-        <x:v>/api/admin/pickups/:id</x:v>
+        <x:v>GET /api/admin/pickups + admin pickup detail</x:v>
       </x:c>
       <x:c r="G45" s="22" t="str">
-        <x:v>Not Tested</x:v>
+        <x:v>Needs Review</x:v>
       </x:c>
       <x:c r="H45" s="22" t="str">
-        <x:v>☐</x:v>
+        <x:v>?</x:v>
       </x:c>
       <x:c r="I45" s="22" t="str">
-        <x:v>High</x:v>
-      </x:c>
-      <x:c r="J45" s="22" t="str"/>
-      <x:c r="K45" s="52" t="str"/>
-      <x:c r="L45" s="22" t="str"/>
-      <x:c r="M45" s="22" t="str"/>
-      <x:c r="N45" s="22" t="str"/>
+        <x:v>Medium</x:v>
+      </x:c>
+      <x:c r="J45" s="22"/>
+      <x:c r="K45" s="52"/>
+      <x:c r="L45" s="22"/>
+      <x:c r="M45" s="22" t="str">
+        <x:v>Was: admin assign collector. Recheck if assignment should be implemented.</x:v>
+      </x:c>
+      <x:c r="N45" s="22"/>
     </x:row>
     <x:row r="46">
       <x:c r="A46" s="22" t="str">
@@ -2638,13 +2659,13 @@
         <x:v>Collector</x:v>
       </x:c>
       <x:c r="D47" s="22" t="str">
-        <x:v>Collector pickup view</x:v>
+        <x:v>Collector pickup experience</x:v>
       </x:c>
       <x:c r="E47" s="22" t="str">
-        <x:v>Collector can open pickup details needed for collection</x:v>
+        <x:v>Collector has available pickup list, my pickup list, slug detail, action workflow, route map, and route preview</x:v>
       </x:c>
       <x:c r="F47" s="22" t="str">
-        <x:v>Collector Pickups</x:v>
+        <x:v>Collector available/my pickups + slug detail + route map</x:v>
       </x:c>
       <x:c r="G47" s="22" t="str">
         <x:v>Not Tested</x:v>
@@ -2653,13 +2674,15 @@
         <x:v>☐</x:v>
       </x:c>
       <x:c r="I47" s="22" t="str">
-        <x:v>High</x:v>
-      </x:c>
-      <x:c r="J47" s="22" t="str"/>
-      <x:c r="K47" s="52" t="str"/>
-      <x:c r="L47" s="22" t="str"/>
-      <x:c r="M47" s="22" t="str"/>
-      <x:c r="N47" s="22" t="str"/>
+        <x:v>Critical</x:v>
+      </x:c>
+      <x:c r="J47" s="22"/>
+      <x:c r="K47" s="52"/>
+      <x:c r="L47" s="22"/>
+      <x:c r="M47" s="22" t="str">
+        <x:v>Expanded from basic pickup view</x:v>
+      </x:c>
+      <x:c r="N47" s="22"/>
     </x:row>
     <x:row r="48">
       <x:c r="A48" s="22" t="str">
@@ -3138,228 +3161,508 @@
       <x:c r="N61" s="22" t="str"/>
     </x:row>
     <x:row r="62">
-      <x:c r="A62" s="22"/>
-      <x:c r="B62" s="22"/>
-      <x:c r="C62" s="22"/>
-      <x:c r="D62" s="22"/>
-      <x:c r="E62" s="22"/>
-      <x:c r="F62" s="22"/>
-      <x:c r="G62" s="22"/>
-      <x:c r="H62" s="22"/>
-      <x:c r="I62" s="22"/>
-      <x:c r="J62" s="22"/>
-      <x:c r="K62" s="52"/>
-      <x:c r="L62" s="22"/>
-      <x:c r="M62" s="22"/>
-      <x:c r="N62" s="22"/>
+      <x:c r="A62" s="56" t="str">
+        <x:v>WG-F061</x:v>
+      </x:c>
+      <x:c r="B62" s="56" t="str">
+        <x:v>Onboarding</x:v>
+      </x:c>
+      <x:c r="C62" s="56" t="str">
+        <x:v>Collector</x:v>
+      </x:c>
+      <x:c r="D62" s="56" t="str">
+        <x:v>Collector location permission onboarding</x:v>
+      </x:c>
+      <x:c r="E62" s="56" t="str">
+        <x:v>Collector onboarding asks for browser location permission before route-fit features depend on location</x:v>
+      </x:c>
+      <x:c r="F62" s="56" t="str">
+        <x:v>Collector onboarding / browser geolocation</x:v>
+      </x:c>
+      <x:c r="G62" s="56" t="str">
+        <x:v>Not Tested</x:v>
+      </x:c>
+      <x:c r="H62" s="56" t="str">
+        <x:v>☐</x:v>
+      </x:c>
+      <x:c r="I62" s="56" t="str">
+        <x:v>Critical</x:v>
+      </x:c>
+      <x:c r="J62" s="56"/>
+      <x:c r="K62" s="57"/>
+      <x:c r="L62" s="56"/>
+      <x:c r="M62" s="56" t="str">
+        <x:v>New collector route-planning dependency</x:v>
+      </x:c>
+      <x:c r="N62" s="56"/>
     </x:row>
     <x:row r="63">
-      <x:c r="A63" s="22"/>
-      <x:c r="B63" s="22"/>
-      <x:c r="C63" s="22"/>
-      <x:c r="D63" s="22"/>
-      <x:c r="E63" s="22"/>
-      <x:c r="F63" s="22"/>
-      <x:c r="G63" s="22"/>
-      <x:c r="H63" s="22"/>
-      <x:c r="I63" s="22"/>
-      <x:c r="J63" s="22"/>
-      <x:c r="K63" s="52"/>
-      <x:c r="L63" s="22"/>
-      <x:c r="M63" s="22"/>
-      <x:c r="N63" s="22"/>
+      <x:c r="A63" s="56" t="str">
+        <x:v>WG-F062</x:v>
+      </x:c>
+      <x:c r="B63" s="56" t="str">
+        <x:v>Onboarding</x:v>
+      </x:c>
+      <x:c r="C63" s="56" t="str">
+        <x:v>Admin</x:v>
+      </x:c>
+      <x:c r="D63" s="56" t="str">
+        <x:v>Admin welcome onboarding flow</x:v>
+      </x:c>
+      <x:c r="E63" s="56" t="str">
+        <x:v>Admin sees and can complete the welcome/onboarding flow without blocking admin pages</x:v>
+      </x:c>
+      <x:c r="F63" s="56" t="str">
+        <x:v>Admin onboarding / dashboard</x:v>
+      </x:c>
+      <x:c r="G63" s="56" t="str">
+        <x:v>Not Tested</x:v>
+      </x:c>
+      <x:c r="H63" s="56" t="str">
+        <x:v>☐</x:v>
+      </x:c>
+      <x:c r="I63" s="56" t="str">
+        <x:v>Medium</x:v>
+      </x:c>
+      <x:c r="J63" s="56"/>
+      <x:c r="K63" s="57"/>
+      <x:c r="L63" s="56"/>
+      <x:c r="M63" s="56" t="str">
+        <x:v>New admin onboarding coverage</x:v>
+      </x:c>
+      <x:c r="N63" s="56"/>
     </x:row>
     <x:row r="64">
-      <x:c r="A64" s="22"/>
-      <x:c r="B64" s="22"/>
-      <x:c r="C64" s="22"/>
-      <x:c r="D64" s="22"/>
-      <x:c r="E64" s="22"/>
-      <x:c r="F64" s="22"/>
-      <x:c r="G64" s="22"/>
-      <x:c r="H64" s="22"/>
-      <x:c r="I64" s="22"/>
-      <x:c r="J64" s="22"/>
-      <x:c r="K64" s="52"/>
-      <x:c r="L64" s="22"/>
-      <x:c r="M64" s="22"/>
-      <x:c r="N64" s="22"/>
+      <x:c r="A64" s="56" t="str">
+        <x:v>WG-F063</x:v>
+      </x:c>
+      <x:c r="B64" s="56" t="str">
+        <x:v>Pickup Detail</x:v>
+      </x:c>
+      <x:c r="C64" s="56" t="str">
+        <x:v>All</x:v>
+      </x:c>
+      <x:c r="D64" s="56" t="str">
+        <x:v>Shared pickup slug detail page</x:v>
+      </x:c>
+      <x:c r="E64" s="56" t="str">
+        <x:v>Customer, admin, and collector slug pickup detail routes reuse the shared detail behavior safely</x:v>
+      </x:c>
+      <x:c r="F64" s="56" t="str">
+        <x:v>Customer/Admin/Collector pickup slug routes</x:v>
+      </x:c>
+      <x:c r="G64" s="56" t="str">
+        <x:v>Not Tested</x:v>
+      </x:c>
+      <x:c r="H64" s="56" t="str">
+        <x:v>☐</x:v>
+      </x:c>
+      <x:c r="I64" s="56" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="J64" s="56"/>
+      <x:c r="K64" s="57"/>
+      <x:c r="L64" s="56"/>
+      <x:c r="M64" s="56" t="str">
+        <x:v>Check role-specific actions/visibility</x:v>
+      </x:c>
+      <x:c r="N64" s="56"/>
     </x:row>
     <x:row r="65">
-      <x:c r="A65" s="22"/>
-      <x:c r="B65" s="22"/>
-      <x:c r="C65" s="22"/>
-      <x:c r="D65" s="22"/>
-      <x:c r="E65" s="22"/>
-      <x:c r="F65" s="22"/>
-      <x:c r="G65" s="22"/>
-      <x:c r="H65" s="22"/>
-      <x:c r="I65" s="22"/>
-      <x:c r="J65" s="22"/>
-      <x:c r="K65" s="52"/>
-      <x:c r="L65" s="22"/>
-      <x:c r="M65" s="22"/>
-      <x:c r="N65" s="22"/>
+      <x:c r="A65" s="56" t="str">
+        <x:v>WG-F064</x:v>
+      </x:c>
+      <x:c r="B65" s="56" t="str">
+        <x:v>Pickup Detail</x:v>
+      </x:c>
+      <x:c r="C65" s="56" t="str">
+        <x:v>All</x:v>
+      </x:c>
+      <x:c r="D65" s="56" t="str">
+        <x:v>Pickup timeline tracker</x:v>
+      </x:c>
+      <x:c r="E65" s="56" t="str">
+        <x:v>Pickup detail shows correct status timeline from PENDING through COMPLETED/CANCELLED</x:v>
+      </x:c>
+      <x:c r="F65" s="56" t="str">
+        <x:v>Pickup detail timeline component</x:v>
+      </x:c>
+      <x:c r="G65" s="56" t="str">
+        <x:v>Not Tested</x:v>
+      </x:c>
+      <x:c r="H65" s="56" t="str">
+        <x:v>☐</x:v>
+      </x:c>
+      <x:c r="I65" s="56" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="J65" s="56"/>
+      <x:c r="K65" s="57"/>
+      <x:c r="L65" s="56"/>
+      <x:c r="M65" s="56" t="str">
+        <x:v>New UI tracker coverage</x:v>
+      </x:c>
+      <x:c r="N65" s="56"/>
     </x:row>
     <x:row r="66">
-      <x:c r="A66" s="22"/>
-      <x:c r="B66" s="22"/>
-      <x:c r="C66" s="22"/>
-      <x:c r="D66" s="22"/>
-      <x:c r="E66" s="22"/>
-      <x:c r="F66" s="22"/>
-      <x:c r="G66" s="22"/>
-      <x:c r="H66" s="22"/>
-      <x:c r="I66" s="22"/>
-      <x:c r="J66" s="22"/>
-      <x:c r="K66" s="52"/>
-      <x:c r="L66" s="22"/>
-      <x:c r="M66" s="22"/>
-      <x:c r="N66" s="22"/>
+      <x:c r="A66" s="56" t="str">
+        <x:v>WG-F065</x:v>
+      </x:c>
+      <x:c r="B66" s="56" t="str">
+        <x:v>Pickup</x:v>
+      </x:c>
+      <x:c r="C66" s="56" t="str">
+        <x:v>Customer</x:v>
+      </x:c>
+      <x:c r="D66" s="56" t="str">
+        <x:v>Cancel blocked after arrived</x:v>
+      </x:c>
+      <x:c r="E66" s="56" t="str">
+        <x:v>Customer cannot cancel once pickup status is ARRIVED or later</x:v>
+      </x:c>
+      <x:c r="F66" s="56" t="str">
+        <x:v>Customer pickup detail cancel action</x:v>
+      </x:c>
+      <x:c r="G66" s="56" t="str">
+        <x:v>Not Tested</x:v>
+      </x:c>
+      <x:c r="H66" s="56" t="str">
+        <x:v>☐</x:v>
+      </x:c>
+      <x:c r="I66" s="56" t="str">
+        <x:v>Critical</x:v>
+      </x:c>
+      <x:c r="J66" s="56"/>
+      <x:c r="K66" s="57"/>
+      <x:c r="L66" s="56"/>
+      <x:c r="M66" s="56" t="str">
+        <x:v>Add UI hidden/disabled and backend guard test</x:v>
+      </x:c>
+      <x:c r="N66" s="56"/>
     </x:row>
     <x:row r="67">
-      <x:c r="A67" s="22"/>
-      <x:c r="B67" s="22"/>
-      <x:c r="C67" s="22"/>
-      <x:c r="D67" s="22"/>
-      <x:c r="E67" s="22"/>
-      <x:c r="F67" s="22"/>
-      <x:c r="G67" s="22"/>
-      <x:c r="H67" s="22"/>
-      <x:c r="I67" s="22"/>
-      <x:c r="J67" s="22"/>
-      <x:c r="K67" s="52"/>
-      <x:c r="L67" s="22"/>
-      <x:c r="M67" s="22"/>
-      <x:c r="N67" s="22"/>
+      <x:c r="A67" s="56" t="str">
+        <x:v>WG-F066</x:v>
+      </x:c>
+      <x:c r="B67" s="56" t="str">
+        <x:v>Pickup Verification</x:v>
+      </x:c>
+      <x:c r="C67" s="56" t="str">
+        <x:v>Customer/Collector</x:v>
+      </x:c>
+      <x:c r="D67" s="56" t="str">
+        <x:v>Estimate vs verified comparison</x:v>
+      </x:c>
+      <x:c r="E67" s="56" t="str">
+        <x:v>Pickup detail compares customer/AI estimate source with collector verified category/weight/points</x:v>
+      </x:c>
+      <x:c r="F67" s="56" t="str">
+        <x:v>Pickup items detail / verification data</x:v>
+      </x:c>
+      <x:c r="G67" s="56" t="str">
+        <x:v>Not Tested</x:v>
+      </x:c>
+      <x:c r="H67" s="56" t="str">
+        <x:v>☐</x:v>
+      </x:c>
+      <x:c r="I67" s="56" t="str">
+        <x:v>Critical</x:v>
+      </x:c>
+      <x:c r="J67" s="56"/>
+      <x:c r="K67" s="57"/>
+      <x:c r="L67" s="56"/>
+      <x:c r="M67" s="56" t="str">
+        <x:v>Important for rewards correctness</x:v>
+      </x:c>
+      <x:c r="N67" s="56"/>
     </x:row>
     <x:row r="68">
-      <x:c r="A68" s="22"/>
-      <x:c r="B68" s="22"/>
-      <x:c r="C68" s="22"/>
-      <x:c r="D68" s="22"/>
-      <x:c r="E68" s="22"/>
-      <x:c r="F68" s="22"/>
-      <x:c r="G68" s="22"/>
-      <x:c r="H68" s="22"/>
-      <x:c r="I68" s="22"/>
-      <x:c r="J68" s="22"/>
-      <x:c r="K68" s="52"/>
-      <x:c r="L68" s="22"/>
-      <x:c r="M68" s="22"/>
-      <x:c r="N68" s="22"/>
+      <x:c r="A68" s="56" t="str">
+        <x:v>WG-F067</x:v>
+      </x:c>
+      <x:c r="B68" s="56" t="str">
+        <x:v>Collector Routing</x:v>
+      </x:c>
+      <x:c r="C68" s="56" t="str">
+        <x:v>Collector</x:v>
+      </x:c>
+      <x:c r="D68" s="56" t="str">
+        <x:v>Available pickups route-fit sorting</x:v>
+      </x:c>
+      <x:c r="E68" s="56" t="str">
+        <x:v>Collector available pickups are sorted by dynamic route fit using current stops and location</x:v>
+      </x:c>
+      <x:c r="F68" s="56" t="str">
+        <x:v>Collector available pickups route planning</x:v>
+      </x:c>
+      <x:c r="G68" s="56" t="str">
+        <x:v>Not Tested</x:v>
+      </x:c>
+      <x:c r="H68" s="56" t="str">
+        <x:v>☐</x:v>
+      </x:c>
+      <x:c r="I68" s="56" t="str">
+        <x:v>Critical</x:v>
+      </x:c>
+      <x:c r="J68" s="56"/>
+      <x:c r="K68" s="57"/>
+      <x:c r="L68" s="56"/>
+      <x:c r="M68" s="56" t="str">
+        <x:v>New collector route-planning work</x:v>
+      </x:c>
+      <x:c r="N68" s="56"/>
     </x:row>
     <x:row r="69">
-      <x:c r="A69" s="22"/>
-      <x:c r="B69" s="22"/>
-      <x:c r="C69" s="22"/>
-      <x:c r="D69" s="22"/>
-      <x:c r="E69" s="22"/>
-      <x:c r="F69" s="22"/>
-      <x:c r="G69" s="22"/>
-      <x:c r="H69" s="22"/>
-      <x:c r="I69" s="22"/>
-      <x:c r="J69" s="22"/>
-      <x:c r="K69" s="52"/>
-      <x:c r="L69" s="22"/>
-      <x:c r="M69" s="22"/>
-      <x:c r="N69" s="22"/>
+      <x:c r="A69" s="56" t="str">
+        <x:v>WG-F068</x:v>
+      </x:c>
+      <x:c r="B69" s="56" t="str">
+        <x:v>Collector Routing</x:v>
+      </x:c>
+      <x:c r="C69" s="56" t="str">
+        <x:v>Collector</x:v>
+      </x:c>
+      <x:c r="D69" s="56" t="str">
+        <x:v>Route-fit labels</x:v>
+      </x:c>
+      <x:c r="E69" s="56" t="str">
+        <x:v>Available pickups show correct labels: Nearest collector, Nearest stop A/B/C, and Off route</x:v>
+      </x:c>
+      <x:c r="F69" s="56" t="str">
+        <x:v>Collector route labels</x:v>
+      </x:c>
+      <x:c r="G69" s="56" t="str">
+        <x:v>Not Tested</x:v>
+      </x:c>
+      <x:c r="H69" s="56" t="str">
+        <x:v>☐</x:v>
+      </x:c>
+      <x:c r="I69" s="56" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="J69" s="56"/>
+      <x:c r="K69" s="57"/>
+      <x:c r="L69" s="56"/>
+      <x:c r="M69" s="56" t="str">
+        <x:v>Label accuracy depends on route calculation</x:v>
+      </x:c>
+      <x:c r="N69" s="56"/>
     </x:row>
     <x:row r="70">
-      <x:c r="A70" s="22"/>
-      <x:c r="B70" s="22"/>
-      <x:c r="C70" s="22"/>
-      <x:c r="D70" s="22"/>
-      <x:c r="E70" s="22"/>
-      <x:c r="F70" s="22"/>
-      <x:c r="G70" s="22"/>
-      <x:c r="H70" s="22"/>
-      <x:c r="I70" s="22"/>
-      <x:c r="J70" s="22"/>
-      <x:c r="K70" s="52"/>
-      <x:c r="L70" s="22"/>
-      <x:c r="M70" s="22"/>
-      <x:c r="N70" s="22"/>
+      <x:c r="A70" s="56" t="str">
+        <x:v>WG-F069</x:v>
+      </x:c>
+      <x:c r="B70" s="56" t="str">
+        <x:v>Collector Routing</x:v>
+      </x:c>
+      <x:c r="C70" s="56" t="str">
+        <x:v>Collector</x:v>
+      </x:c>
+      <x:c r="D70" s="56" t="str">
+        <x:v>Multiple accepted pickups</x:v>
+      </x:c>
+      <x:c r="E70" s="56" t="str">
+        <x:v>Collector can accept and manage multiple active pickups as a multi-stop route</x:v>
+      </x:c>
+      <x:c r="F70" s="56" t="str">
+        <x:v>Collector my pickups / accepted stops</x:v>
+      </x:c>
+      <x:c r="G70" s="56" t="str">
+        <x:v>Not Tested</x:v>
+      </x:c>
+      <x:c r="H70" s="56" t="str">
+        <x:v>☐</x:v>
+      </x:c>
+      <x:c r="I70" s="56" t="str">
+        <x:v>Critical</x:v>
+      </x:c>
+      <x:c r="J70" s="56"/>
+      <x:c r="K70" s="57"/>
+      <x:c r="L70" s="56"/>
+      <x:c r="M70" s="56" t="str">
+        <x:v>New multi-stop behavior</x:v>
+      </x:c>
+      <x:c r="N70" s="56"/>
     </x:row>
     <x:row r="71">
-      <x:c r="A71" s="22"/>
-      <x:c r="B71" s="22"/>
-      <x:c r="C71" s="22"/>
-      <x:c r="D71" s="22"/>
-      <x:c r="E71" s="22"/>
-      <x:c r="F71" s="22"/>
-      <x:c r="G71" s="22"/>
-      <x:c r="H71" s="22"/>
-      <x:c r="I71" s="22"/>
-      <x:c r="J71" s="22"/>
-      <x:c r="K71" s="52"/>
-      <x:c r="L71" s="22"/>
-      <x:c r="M71" s="22"/>
-      <x:c r="N71" s="22"/>
+      <x:c r="A71" s="56" t="str">
+        <x:v>WG-F070</x:v>
+      </x:c>
+      <x:c r="B71" s="56" t="str">
+        <x:v>Collector Routing</x:v>
+      </x:c>
+      <x:c r="C71" s="56" t="str">
+        <x:v>Collector</x:v>
+      </x:c>
+      <x:c r="D71" s="56" t="str">
+        <x:v>My Pickups multi-stop route map</x:v>
+      </x:c>
+      <x:c r="E71" s="56" t="str">
+        <x:v>Collector My Pickups shows all accepted stops on one route map without marker drift</x:v>
+      </x:c>
+      <x:c r="F71" s="56" t="str">
+        <x:v>Collector My Pickups route map</x:v>
+      </x:c>
+      <x:c r="G71" s="56" t="str">
+        <x:v>Not Tested</x:v>
+      </x:c>
+      <x:c r="H71" s="56" t="str">
+        <x:v>☐</x:v>
+      </x:c>
+      <x:c r="I71" s="56" t="str">
+        <x:v>Critical</x:v>
+      </x:c>
+      <x:c r="J71" s="56"/>
+      <x:c r="K71" s="57"/>
+      <x:c r="L71" s="56"/>
+      <x:c r="M71" s="56" t="str">
+        <x:v>Map rendering and ordering coverage</x:v>
+      </x:c>
+      <x:c r="N71" s="56"/>
     </x:row>
     <x:row r="72">
-      <x:c r="A72" s="22"/>
-      <x:c r="B72" s="22"/>
-      <x:c r="C72" s="22"/>
-      <x:c r="D72" s="22"/>
-      <x:c r="E72" s="22"/>
-      <x:c r="F72" s="22"/>
-      <x:c r="G72" s="22"/>
-      <x:c r="H72" s="22"/>
-      <x:c r="I72" s="22"/>
-      <x:c r="J72" s="22"/>
-      <x:c r="K72" s="52"/>
-      <x:c r="L72" s="22"/>
-      <x:c r="M72" s="22"/>
-      <x:c r="N72" s="22"/>
+      <x:c r="A72" s="56" t="str">
+        <x:v>WG-F071</x:v>
+      </x:c>
+      <x:c r="B72" s="56" t="str">
+        <x:v>Collector Routing</x:v>
+      </x:c>
+      <x:c r="C72" s="56" t="str">
+        <x:v>Collector</x:v>
+      </x:c>
+      <x:c r="D72" s="56" t="str">
+        <x:v>Accept pickup route preview dialog</x:v>
+      </x:c>
+      <x:c r="E72" s="56" t="str">
+        <x:v>Before accepting, dialog previews current stops plus the new pickup and final route impact</x:v>
+      </x:c>
+      <x:c r="F72" s="56" t="str">
+        <x:v>Accept pickup dialog / route preview</x:v>
+      </x:c>
+      <x:c r="G72" s="56" t="str">
+        <x:v>Not Tested</x:v>
+      </x:c>
+      <x:c r="H72" s="56" t="str">
+        <x:v>☐</x:v>
+      </x:c>
+      <x:c r="I72" s="56" t="str">
+        <x:v>Critical</x:v>
+      </x:c>
+      <x:c r="J72" s="56"/>
+      <x:c r="K72" s="57"/>
+      <x:c r="L72" s="56"/>
+      <x:c r="M72" s="56" t="str">
+        <x:v>Must test before confirm</x:v>
+      </x:c>
+      <x:c r="N72" s="56"/>
     </x:row>
     <x:row r="73">
-      <x:c r="A73" s="22"/>
-      <x:c r="B73" s="22"/>
-      <x:c r="C73" s="22"/>
-      <x:c r="D73" s="22"/>
-      <x:c r="E73" s="22"/>
-      <x:c r="F73" s="22"/>
-      <x:c r="G73" s="22"/>
-      <x:c r="H73" s="22"/>
-      <x:c r="I73" s="22"/>
-      <x:c r="J73" s="22"/>
-      <x:c r="K73" s="52"/>
-      <x:c r="L73" s="22"/>
-      <x:c r="M73" s="22"/>
-      <x:c r="N73" s="22"/>
+      <x:c r="A73" s="56" t="str">
+        <x:v>WG-F072</x:v>
+      </x:c>
+      <x:c r="B73" s="56" t="str">
+        <x:v>Maps</x:v>
+      </x:c>
+      <x:c r="C73" s="56" t="str">
+        <x:v>Collector</x:v>
+      </x:c>
+      <x:c r="D73" s="56" t="str">
+        <x:v>MapLibre/OSRM route map component</x:v>
+      </x:c>
+      <x:c r="E73" s="56" t="str">
+        <x:v>MapLibre/OSRM component renders route and stops correctly instead of embedded Google Maps</x:v>
+      </x:c>
+      <x:c r="F73" s="56" t="str">
+        <x:v>MapLibre + OSRM route map component</x:v>
+      </x:c>
+      <x:c r="G73" s="56" t="str">
+        <x:v>Not Tested</x:v>
+      </x:c>
+      <x:c r="H73" s="56" t="str">
+        <x:v>☐</x:v>
+      </x:c>
+      <x:c r="I73" s="56" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="J73" s="56"/>
+      <x:c r="K73" s="57"/>
+      <x:c r="L73" s="56"/>
+      <x:c r="M73" s="56" t="str">
+        <x:v>Replacement map implementation</x:v>
+      </x:c>
+      <x:c r="N73" s="56"/>
     </x:row>
     <x:row r="74">
-      <x:c r="A74" s="22"/>
-      <x:c r="B74" s="22"/>
-      <x:c r="C74" s="22"/>
-      <x:c r="D74" s="22"/>
-      <x:c r="E74" s="22"/>
-      <x:c r="F74" s="22"/>
-      <x:c r="G74" s="22"/>
-      <x:c r="H74" s="22"/>
-      <x:c r="I74" s="22"/>
-      <x:c r="J74" s="22"/>
-      <x:c r="K74" s="52"/>
-      <x:c r="L74" s="22"/>
-      <x:c r="M74" s="22"/>
-      <x:c r="N74" s="22"/>
+      <x:c r="A74" s="56" t="str">
+        <x:v>WG-F073</x:v>
+      </x:c>
+      <x:c r="B74" s="56" t="str">
+        <x:v>Collector Routing</x:v>
+      </x:c>
+      <x:c r="C74" s="56" t="str">
+        <x:v>Collector</x:v>
+      </x:c>
+      <x:c r="D74" s="56" t="str">
+        <x:v>Route recalculation after accepted stops</x:v>
+      </x:c>
+      <x:c r="E74" s="56" t="str">
+        <x:v>Available pickup order recalculates after collector already has active accepted stops</x:v>
+      </x:c>
+      <x:c r="F74" s="56" t="str">
+        <x:v>Collector available pickups sorting</x:v>
+      </x:c>
+      <x:c r="G74" s="56" t="str">
+        <x:v>Not Tested</x:v>
+      </x:c>
+      <x:c r="H74" s="56" t="str">
+        <x:v>☐</x:v>
+      </x:c>
+      <x:c r="I74" s="56" t="str">
+        <x:v>Critical</x:v>
+      </x:c>
+      <x:c r="J74" s="56"/>
+      <x:c r="K74" s="57"/>
+      <x:c r="L74" s="56"/>
+      <x:c r="M74" s="56" t="str">
+        <x:v>Prevents stale ordering</x:v>
+      </x:c>
+      <x:c r="N74" s="56"/>
     </x:row>
     <x:row r="75">
-      <x:c r="A75" s="22"/>
-      <x:c r="B75" s="22"/>
-      <x:c r="C75" s="22"/>
-      <x:c r="D75" s="22"/>
-      <x:c r="E75" s="22"/>
-      <x:c r="F75" s="22"/>
-      <x:c r="G75" s="22"/>
-      <x:c r="H75" s="22"/>
-      <x:c r="I75" s="22"/>
-      <x:c r="J75" s="22"/>
-      <x:c r="K75" s="52"/>
-      <x:c r="L75" s="22"/>
-      <x:c r="M75" s="22"/>
-      <x:c r="N75" s="22"/>
+      <x:c r="A75" s="56" t="str">
+        <x:v>WG-F074</x:v>
+      </x:c>
+      <x:c r="B75" s="56" t="str">
+        <x:v>Pickup Detail</x:v>
+      </x:c>
+      <x:c r="C75" s="56" t="str">
+        <x:v>Admin/Collector</x:v>
+      </x:c>
+      <x:c r="D75" s="56" t="str">
+        <x:v>Admin and collector slug page render</x:v>
+      </x:c>
+      <x:c r="E75" s="56" t="str">
+        <x:v>Admin and collector pickup slug/detail pages render without route guard or resolver errors</x:v>
+      </x:c>
+      <x:c r="F75" s="56" t="str">
+        <x:v>Admin/Collector pickup slug routes</x:v>
+      </x:c>
+      <x:c r="G75" s="56" t="str">
+        <x:v>Not Tested</x:v>
+      </x:c>
+      <x:c r="H75" s="56" t="str">
+        <x:v>☐</x:v>
+      </x:c>
+      <x:c r="I75" s="56" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="J75" s="56"/>
+      <x:c r="K75" s="57"/>
+      <x:c r="L75" s="56"/>
+      <x:c r="M75" s="56" t="str">
+        <x:v>New route coverage</x:v>
+      </x:c>
+      <x:c r="N75" s="56"/>
     </x:row>
     <x:row r="76">
       <x:c r="A76" s="22"/>
@@ -5381,13 +5684,13 @@
   </x:conditionalFormatting>
   <x:dataValidations count="4">
     <x:dataValidation type="list" sqref="G2:G200">
-      <x:formula1>Lists!$A$2:$A$7</x:formula1>
+      <x:formula1>"Not Tested,In Progress,Passed,Failed,Blocked,Needs Review"</x:formula1>
     </x:dataValidation>
     <x:dataValidation type="list" sqref="H2:H200">
-      <x:formula1>Lists!$B$2:$B$7</x:formula1>
+      <x:formula1>"☐,☑,☒,⚠,?"</x:formula1>
     </x:dataValidation>
     <x:dataValidation type="list" sqref="I2:I200">
-      <x:formula1>Lists!$C$2:$C$5</x:formula1>
+      <x:formula1>"Critical,High,Medium,Low"</x:formula1>
     </x:dataValidation>
     <x:dataValidation type="list" sqref="C2:C200">
       <x:formula1>Lists!$D$2:$D$7</x:formula1>
@@ -5395,7 +5698,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc45f4e4cf7484cab"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R653d15c451b64bec"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5404,20 +5707,20 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="12" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="12" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="18" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="12" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="14" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="38" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="38" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="32" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="32" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="16" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="14" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="16" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="16" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="32" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="7.940000057220459" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="11.039999961853027" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="9.020000457763672" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="9.289999961853027" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="7.670000076293945" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="30" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="30" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="30" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="30" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="8.210000038146973" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="11.979999542236328" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="9.020000457763672" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="13.319999694824219" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="30" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -5465,104 +5768,88 @@
       </x:c>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" s="22" t="str">
+      <x:c r="A2" s="56" t="str">
         <x:v>BUG-001</x:v>
       </x:c>
-      <x:c r="B2" s="22" t="str"/>
-      <x:c r="C2" s="22" t="str"/>
-      <x:c r="D2" s="22" t="str"/>
-      <x:c r="E2" s="22" t="str">
-        <x:v>Open</x:v>
-      </x:c>
-      <x:c r="F2" s="22" t="str"/>
-      <x:c r="G2" s="22" t="str"/>
-      <x:c r="H2" s="22" t="str"/>
-      <x:c r="I2" s="22" t="str"/>
-      <x:c r="J2" s="22" t="str"/>
-      <x:c r="K2" s="52" t="str"/>
-      <x:c r="L2" s="22" t="str"/>
-      <x:c r="M2" s="22" t="str"/>
-      <x:c r="N2" s="22" t="str"/>
+      <x:c r="B2" s="56"/>
+      <x:c r="C2" s="56"/>
+      <x:c r="D2" s="56"/>
+      <x:c r="E2" s="56"/>
+      <x:c r="F2" s="56" t="str">
+        <x:v>Use this first row only when a real bug is found</x:v>
+      </x:c>
+      <x:c r="G2" s="56"/>
+      <x:c r="H2" s="56"/>
+      <x:c r="I2" s="56"/>
+      <x:c r="J2" s="56"/>
+      <x:c r="K2" s="57"/>
+      <x:c r="L2" s="56"/>
+      <x:c r="M2" s="56"/>
+      <x:c r="N2" s="56"/>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="22" t="str">
-        <x:v>BUG-002</x:v>
-      </x:c>
-      <x:c r="B3" s="22" t="str"/>
-      <x:c r="C3" s="22" t="str"/>
-      <x:c r="D3" s="22" t="str"/>
-      <x:c r="E3" s="22" t="str">
-        <x:v>Open</x:v>
-      </x:c>
-      <x:c r="F3" s="22" t="str"/>
-      <x:c r="G3" s="22" t="str"/>
-      <x:c r="H3" s="22" t="str"/>
-      <x:c r="I3" s="22" t="str"/>
-      <x:c r="J3" s="22" t="str"/>
-      <x:c r="K3" s="52" t="str"/>
-      <x:c r="L3" s="22" t="str"/>
-      <x:c r="M3" s="22" t="str"/>
-      <x:c r="N3" s="22" t="str"/>
+      <x:c r="A3" s="22"/>
+      <x:c r="B3" s="22"/>
+      <x:c r="C3" s="22"/>
+      <x:c r="D3" s="22"/>
+      <x:c r="E3" s="22"/>
+      <x:c r="F3" s="22"/>
+      <x:c r="G3" s="22"/>
+      <x:c r="H3" s="22"/>
+      <x:c r="I3" s="22"/>
+      <x:c r="J3" s="22"/>
+      <x:c r="K3" s="52"/>
+      <x:c r="L3" s="22"/>
+      <x:c r="M3" s="22"/>
+      <x:c r="N3" s="22"/>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="22" t="str">
-        <x:v>BUG-003</x:v>
-      </x:c>
-      <x:c r="B4" s="22" t="str"/>
-      <x:c r="C4" s="22" t="str"/>
-      <x:c r="D4" s="22" t="str"/>
-      <x:c r="E4" s="22" t="str">
-        <x:v>Open</x:v>
-      </x:c>
-      <x:c r="F4" s="22" t="str"/>
-      <x:c r="G4" s="22" t="str"/>
-      <x:c r="H4" s="22" t="str"/>
-      <x:c r="I4" s="22" t="str"/>
-      <x:c r="J4" s="22" t="str"/>
-      <x:c r="K4" s="52" t="str"/>
-      <x:c r="L4" s="22" t="str"/>
-      <x:c r="M4" s="22" t="str"/>
-      <x:c r="N4" s="22" t="str"/>
+      <x:c r="A4" s="22"/>
+      <x:c r="B4" s="22"/>
+      <x:c r="C4" s="22"/>
+      <x:c r="D4" s="22"/>
+      <x:c r="E4" s="22"/>
+      <x:c r="F4" s="22"/>
+      <x:c r="G4" s="22"/>
+      <x:c r="H4" s="22"/>
+      <x:c r="I4" s="22"/>
+      <x:c r="J4" s="22"/>
+      <x:c r="K4" s="52"/>
+      <x:c r="L4" s="22"/>
+      <x:c r="M4" s="22"/>
+      <x:c r="N4" s="22"/>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="22" t="str">
-        <x:v>BUG-004</x:v>
-      </x:c>
-      <x:c r="B5" s="22" t="str"/>
-      <x:c r="C5" s="22" t="str"/>
-      <x:c r="D5" s="22" t="str"/>
-      <x:c r="E5" s="22" t="str">
-        <x:v>Open</x:v>
-      </x:c>
-      <x:c r="F5" s="22" t="str"/>
-      <x:c r="G5" s="22" t="str"/>
-      <x:c r="H5" s="22" t="str"/>
-      <x:c r="I5" s="22" t="str"/>
-      <x:c r="J5" s="22" t="str"/>
-      <x:c r="K5" s="52" t="str"/>
-      <x:c r="L5" s="22" t="str"/>
-      <x:c r="M5" s="22" t="str"/>
-      <x:c r="N5" s="22" t="str"/>
+      <x:c r="A5" s="22"/>
+      <x:c r="B5" s="22"/>
+      <x:c r="C5" s="22"/>
+      <x:c r="D5" s="22"/>
+      <x:c r="E5" s="22"/>
+      <x:c r="F5" s="22"/>
+      <x:c r="G5" s="22"/>
+      <x:c r="H5" s="22"/>
+      <x:c r="I5" s="22"/>
+      <x:c r="J5" s="22"/>
+      <x:c r="K5" s="52"/>
+      <x:c r="L5" s="22"/>
+      <x:c r="M5" s="22"/>
+      <x:c r="N5" s="22"/>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="22" t="str">
-        <x:v>BUG-005</x:v>
-      </x:c>
-      <x:c r="B6" s="22" t="str"/>
-      <x:c r="C6" s="22" t="str"/>
-      <x:c r="D6" s="22" t="str"/>
-      <x:c r="E6" s="22" t="str">
-        <x:v>Open</x:v>
-      </x:c>
-      <x:c r="F6" s="22" t="str"/>
-      <x:c r="G6" s="22" t="str"/>
-      <x:c r="H6" s="22" t="str"/>
-      <x:c r="I6" s="22" t="str"/>
-      <x:c r="J6" s="22" t="str"/>
-      <x:c r="K6" s="52" t="str"/>
-      <x:c r="L6" s="22" t="str"/>
-      <x:c r="M6" s="22" t="str"/>
-      <x:c r="N6" s="22" t="str"/>
+      <x:c r="A6" s="22"/>
+      <x:c r="B6" s="22"/>
+      <x:c r="C6" s="22"/>
+      <x:c r="D6" s="22"/>
+      <x:c r="E6" s="22"/>
+      <x:c r="F6" s="22"/>
+      <x:c r="G6" s="22"/>
+      <x:c r="H6" s="22"/>
+      <x:c r="I6" s="22"/>
+      <x:c r="J6" s="22"/>
+      <x:c r="K6" s="52"/>
+      <x:c r="L6" s="22"/>
+      <x:c r="M6" s="22"/>
+      <x:c r="N6" s="22"/>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="22"/>
@@ -8682,18 +8969,18 @@
   </x:conditionalFormatting>
   <x:dataValidations count="3">
     <x:dataValidation type="list" sqref="D2:D200">
-      <x:formula1>Lists!$E$2:$E$5</x:formula1>
+      <x:formula1>"Critical,High,Medium,Low"</x:formula1>
     </x:dataValidation>
     <x:dataValidation type="list" sqref="E2:E200">
-      <x:formula1>Lists!$F$2:$F$7</x:formula1>
+      <x:formula1>"Open,In Progress,Fixed,Closed,Won’t Fix,Duplicate"</x:formula1>
     </x:dataValidation>
     <x:dataValidation type="list" sqref="M2:M200">
-      <x:formula1>Lists!$H$2:$H$5</x:formula1>
+      <x:formula1>"Not Retested,Passed,Failed,Blocked"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R67f8b155f4944278"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf12a90914b714f31"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8702,17 +8989,17 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="12" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="12" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="18" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="15" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="28" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="34" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="40" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="34" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="34" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="14" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="12" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="8.079999923706055" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="11.039999961853027" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="14.670000076293945" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="15.609999656677246" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="30" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="30" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="30" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="30" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="13.319999694824219" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="8.609999656677246" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="7.940000057220459" hidden="0" customWidth="1"/>
     <x:col min="12" max="12" width="30" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
@@ -9117,26 +9404,28 @@
         <x:v>Pickup Lifecycle</x:v>
       </x:c>
       <x:c r="D13" s="22" t="str">
-        <x:v>Collector/Admin</x:v>
+        <x:v>Collector</x:v>
       </x:c>
       <x:c r="E13" s="22" t="str">
-        <x:v>Verify actual pickup weight</x:v>
+        <x:v>Verify actual pickup values</x:v>
       </x:c>
       <x:c r="F13" s="22" t="str">
         <x:v>Pickup status ARRIVED</x:v>
       </x:c>
       <x:c r="G13" s="22" t="str">
-        <x:v>Enter actual weight/category and submit</x:v>
+        <x:v>Collector enters actual weight/category and submits verification</x:v>
       </x:c>
       <x:c r="H13" s="22" t="str">
         <x:v>Pickup moves to VERIFIED and actual values persist</x:v>
       </x:c>
-      <x:c r="I13" s="22" t="str"/>
+      <x:c r="I13" s="22"/>
       <x:c r="J13" s="22" t="str">
         <x:v>Not Run</x:v>
       </x:c>
-      <x:c r="K13" s="22" t="str"/>
-      <x:c r="L13" s="22" t="str"/>
+      <x:c r="K13" s="22"/>
+      <x:c r="L13" s="22" t="str">
+        <x:v>Collector-side lifecycle only</x:v>
+      </x:c>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="22" t="str">
@@ -9235,200 +9524,452 @@
       <x:c r="L16" s="22" t="str"/>
     </x:row>
     <x:row r="17">
-      <x:c r="A17" s="22"/>
-      <x:c r="B17" s="22"/>
-      <x:c r="C17" s="22"/>
-      <x:c r="D17" s="22"/>
-      <x:c r="E17" s="22"/>
-      <x:c r="F17" s="22"/>
-      <x:c r="G17" s="22"/>
-      <x:c r="H17" s="22"/>
-      <x:c r="I17" s="22"/>
-      <x:c r="J17" s="22"/>
-      <x:c r="K17" s="22"/>
-      <x:c r="L17" s="22"/>
+      <x:c r="A17" s="56" t="str">
+        <x:v>TC-016</x:v>
+      </x:c>
+      <x:c r="B17" s="56" t="str">
+        <x:v>WG-F061</x:v>
+      </x:c>
+      <x:c r="C17" s="56" t="str">
+        <x:v>Onboarding</x:v>
+      </x:c>
+      <x:c r="D17" s="56" t="str">
+        <x:v>Collector</x:v>
+      </x:c>
+      <x:c r="E17" s="56" t="str">
+        <x:v>Ask browser location permission first</x:v>
+      </x:c>
+      <x:c r="F17" s="56" t="str">
+        <x:v>Logged in as new COLLECTOR</x:v>
+      </x:c>
+      <x:c r="G17" s="56" t="str">
+        <x:v>Open collector onboarding</x:v>
+      </x:c>
+      <x:c r="H17" s="56" t="str">
+        <x:v>Browser location permission prompt/step appears before route-fit setup</x:v>
+      </x:c>
+      <x:c r="I17" s="56"/>
+      <x:c r="J17" s="56" t="str">
+        <x:v>Not Run</x:v>
+      </x:c>
+      <x:c r="K17" s="56"/>
+      <x:c r="L17" s="56"/>
     </x:row>
     <x:row r="18">
-      <x:c r="A18" s="22"/>
-      <x:c r="B18" s="22"/>
-      <x:c r="C18" s="22"/>
-      <x:c r="D18" s="22"/>
-      <x:c r="E18" s="22"/>
-      <x:c r="F18" s="22"/>
-      <x:c r="G18" s="22"/>
-      <x:c r="H18" s="22"/>
-      <x:c r="I18" s="22"/>
-      <x:c r="J18" s="22"/>
-      <x:c r="K18" s="22"/>
-      <x:c r="L18" s="22"/>
+      <x:c r="A18" s="56" t="str">
+        <x:v>TC-017</x:v>
+      </x:c>
+      <x:c r="B18" s="56" t="str">
+        <x:v>WG-F062</x:v>
+      </x:c>
+      <x:c r="C18" s="56" t="str">
+        <x:v>Onboarding</x:v>
+      </x:c>
+      <x:c r="D18" s="56" t="str">
+        <x:v>Admin</x:v>
+      </x:c>
+      <x:c r="E18" s="56" t="str">
+        <x:v>Admin onboarding welcome flow</x:v>
+      </x:c>
+      <x:c r="F18" s="56" t="str">
+        <x:v>Logged in as new ADMIN</x:v>
+      </x:c>
+      <x:c r="G18" s="56" t="str">
+        <x:v>Open admin dashboard/onboarding path</x:v>
+      </x:c>
+      <x:c r="H18" s="56" t="str">
+        <x:v>Admin welcome flow renders and can be completed</x:v>
+      </x:c>
+      <x:c r="I18" s="56"/>
+      <x:c r="J18" s="56" t="str">
+        <x:v>Not Run</x:v>
+      </x:c>
+      <x:c r="K18" s="56"/>
+      <x:c r="L18" s="56"/>
     </x:row>
     <x:row r="19">
-      <x:c r="A19" s="22"/>
-      <x:c r="B19" s="22"/>
-      <x:c r="C19" s="22"/>
-      <x:c r="D19" s="22"/>
-      <x:c r="E19" s="22"/>
-      <x:c r="F19" s="22"/>
-      <x:c r="G19" s="22"/>
-      <x:c r="H19" s="22"/>
-      <x:c r="I19" s="22"/>
-      <x:c r="J19" s="22"/>
-      <x:c r="K19" s="22"/>
-      <x:c r="L19" s="22"/>
+      <x:c r="A19" s="56" t="str">
+        <x:v>TC-018</x:v>
+      </x:c>
+      <x:c r="B19" s="56" t="str">
+        <x:v>WG-F063</x:v>
+      </x:c>
+      <x:c r="C19" s="56" t="str">
+        <x:v>Pickup Detail</x:v>
+      </x:c>
+      <x:c r="D19" s="56" t="str">
+        <x:v>All</x:v>
+      </x:c>
+      <x:c r="E19" s="56" t="str">
+        <x:v>Shared pickup detail by role</x:v>
+      </x:c>
+      <x:c r="F19" s="56" t="str">
+        <x:v>Pickup exists; login as customer/admin/collector separately</x:v>
+      </x:c>
+      <x:c r="G19" s="56" t="str">
+        <x:v>Open each role slug/detail route</x:v>
+      </x:c>
+      <x:c r="H19" s="56" t="str">
+        <x:v>Shared detail renders with correct role-specific actions</x:v>
+      </x:c>
+      <x:c r="I19" s="56"/>
+      <x:c r="J19" s="56" t="str">
+        <x:v>Not Run</x:v>
+      </x:c>
+      <x:c r="K19" s="56"/>
+      <x:c r="L19" s="56"/>
     </x:row>
     <x:row r="20">
-      <x:c r="A20" s="22"/>
-      <x:c r="B20" s="22"/>
-      <x:c r="C20" s="22"/>
-      <x:c r="D20" s="22"/>
-      <x:c r="E20" s="22"/>
-      <x:c r="F20" s="22"/>
-      <x:c r="G20" s="22"/>
-      <x:c r="H20" s="22"/>
-      <x:c r="I20" s="22"/>
-      <x:c r="J20" s="22"/>
-      <x:c r="K20" s="22"/>
-      <x:c r="L20" s="22"/>
+      <x:c r="A20" s="56" t="str">
+        <x:v>TC-019</x:v>
+      </x:c>
+      <x:c r="B20" s="56" t="str">
+        <x:v>WG-F064</x:v>
+      </x:c>
+      <x:c r="C20" s="56" t="str">
+        <x:v>Pickup Detail</x:v>
+      </x:c>
+      <x:c r="D20" s="56" t="str">
+        <x:v>All</x:v>
+      </x:c>
+      <x:c r="E20" s="56" t="str">
+        <x:v>Pickup timeline status tracker</x:v>
+      </x:c>
+      <x:c r="F20" s="56" t="str">
+        <x:v>Pickup exists in each status</x:v>
+      </x:c>
+      <x:c r="G20" s="56" t="str">
+        <x:v>Open pickup detail</x:v>
+      </x:c>
+      <x:c r="H20" s="56" t="str">
+        <x:v>Timeline highlights current status and history correctly</x:v>
+      </x:c>
+      <x:c r="I20" s="56"/>
+      <x:c r="J20" s="56" t="str">
+        <x:v>Not Run</x:v>
+      </x:c>
+      <x:c r="K20" s="56"/>
+      <x:c r="L20" s="56"/>
     </x:row>
     <x:row r="21">
-      <x:c r="A21" s="22"/>
-      <x:c r="B21" s="22"/>
-      <x:c r="C21" s="22"/>
-      <x:c r="D21" s="22"/>
-      <x:c r="E21" s="22"/>
-      <x:c r="F21" s="22"/>
-      <x:c r="G21" s="22"/>
-      <x:c r="H21" s="22"/>
-      <x:c r="I21" s="22"/>
-      <x:c r="J21" s="22"/>
-      <x:c r="K21" s="22"/>
-      <x:c r="L21" s="22"/>
+      <x:c r="A21" s="56" t="str">
+        <x:v>TC-020</x:v>
+      </x:c>
+      <x:c r="B21" s="56" t="str">
+        <x:v>WG-F065</x:v>
+      </x:c>
+      <x:c r="C21" s="56" t="str">
+        <x:v>Pickup</x:v>
+      </x:c>
+      <x:c r="D21" s="56" t="str">
+        <x:v>Customer</x:v>
+      </x:c>
+      <x:c r="E21" s="56" t="str">
+        <x:v>Cancel hidden/blocked after arrived</x:v>
+      </x:c>
+      <x:c r="F21" s="56" t="str">
+        <x:v>Pickup status ARRIVED</x:v>
+      </x:c>
+      <x:c r="G21" s="56" t="str">
+        <x:v>Open customer pickup detail and try cancel endpoint/UI</x:v>
+      </x:c>
+      <x:c r="H21" s="56" t="str">
+        <x:v>Cancel is hidden/disabled or backend rejects; status unchanged</x:v>
+      </x:c>
+      <x:c r="I21" s="56"/>
+      <x:c r="J21" s="56" t="str">
+        <x:v>Not Run</x:v>
+      </x:c>
+      <x:c r="K21" s="56"/>
+      <x:c r="L21" s="56"/>
     </x:row>
     <x:row r="22">
-      <x:c r="A22" s="22"/>
-      <x:c r="B22" s="22"/>
-      <x:c r="C22" s="22"/>
-      <x:c r="D22" s="22"/>
-      <x:c r="E22" s="22"/>
-      <x:c r="F22" s="22"/>
-      <x:c r="G22" s="22"/>
-      <x:c r="H22" s="22"/>
-      <x:c r="I22" s="22"/>
-      <x:c r="J22" s="22"/>
-      <x:c r="K22" s="22"/>
-      <x:c r="L22" s="22"/>
+      <x:c r="A22" s="56" t="str">
+        <x:v>TC-021</x:v>
+      </x:c>
+      <x:c r="B22" s="56" t="str">
+        <x:v>WG-F066</x:v>
+      </x:c>
+      <x:c r="C22" s="56" t="str">
+        <x:v>Pickup Verification</x:v>
+      </x:c>
+      <x:c r="D22" s="56" t="str">
+        <x:v>Customer/Collector</x:v>
+      </x:c>
+      <x:c r="E22" s="56" t="str">
+        <x:v>Show estimate source vs verified values</x:v>
+      </x:c>
+      <x:c r="F22" s="56" t="str">
+        <x:v>Pickup has AI/customer estimate and collector verified values</x:v>
+      </x:c>
+      <x:c r="G22" s="56" t="str">
+        <x:v>Open pickup detail after verification</x:v>
+      </x:c>
+      <x:c r="H22" s="56" t="str">
+        <x:v>Customer/AI estimate and collector verified values are visible and distinct</x:v>
+      </x:c>
+      <x:c r="I22" s="56"/>
+      <x:c r="J22" s="56" t="str">
+        <x:v>Not Run</x:v>
+      </x:c>
+      <x:c r="K22" s="56"/>
+      <x:c r="L22" s="56"/>
     </x:row>
     <x:row r="23">
-      <x:c r="A23" s="22"/>
-      <x:c r="B23" s="22"/>
-      <x:c r="C23" s="22"/>
-      <x:c r="D23" s="22"/>
-      <x:c r="E23" s="22"/>
-      <x:c r="F23" s="22"/>
-      <x:c r="G23" s="22"/>
-      <x:c r="H23" s="22"/>
-      <x:c r="I23" s="22"/>
-      <x:c r="J23" s="22"/>
-      <x:c r="K23" s="22"/>
-      <x:c r="L23" s="22"/>
+      <x:c r="A23" s="56" t="str">
+        <x:v>TC-022</x:v>
+      </x:c>
+      <x:c r="B23" s="56" t="str">
+        <x:v>WG-F069</x:v>
+      </x:c>
+      <x:c r="C23" s="56" t="str">
+        <x:v>Collector Routing</x:v>
+      </x:c>
+      <x:c r="D23" s="56" t="str">
+        <x:v>Collector</x:v>
+      </x:c>
+      <x:c r="E23" s="56" t="str">
+        <x:v>Accept multiple pickups</x:v>
+      </x:c>
+      <x:c r="F23" s="56" t="str">
+        <x:v>Collector has one accepted pickup; another pending pickup exists</x:v>
+      </x:c>
+      <x:c r="G23" s="56" t="str">
+        <x:v>Accept second pickup</x:v>
+      </x:c>
+      <x:c r="H23" s="56" t="str">
+        <x:v>Both pickups appear under My Pickups and route map includes both stops</x:v>
+      </x:c>
+      <x:c r="I23" s="56"/>
+      <x:c r="J23" s="56" t="str">
+        <x:v>Not Run</x:v>
+      </x:c>
+      <x:c r="K23" s="56"/>
+      <x:c r="L23" s="56"/>
     </x:row>
     <x:row r="24">
-      <x:c r="A24" s="22"/>
-      <x:c r="B24" s="22"/>
-      <x:c r="C24" s="22"/>
-      <x:c r="D24" s="22"/>
-      <x:c r="E24" s="22"/>
-      <x:c r="F24" s="22"/>
-      <x:c r="G24" s="22"/>
-      <x:c r="H24" s="22"/>
-      <x:c r="I24" s="22"/>
-      <x:c r="J24" s="22"/>
-      <x:c r="K24" s="22"/>
-      <x:c r="L24" s="22"/>
+      <x:c r="A24" s="56" t="str">
+        <x:v>TC-023</x:v>
+      </x:c>
+      <x:c r="B24" s="56" t="str">
+        <x:v>WG-F073</x:v>
+      </x:c>
+      <x:c r="C24" s="56" t="str">
+        <x:v>Collector Routing</x:v>
+      </x:c>
+      <x:c r="D24" s="56" t="str">
+        <x:v>Collector</x:v>
+      </x:c>
+      <x:c r="E24" s="56" t="str">
+        <x:v>Available pickups reorder after active stops</x:v>
+      </x:c>
+      <x:c r="F24" s="56" t="str">
+        <x:v>Collector has active stops and several available pickups</x:v>
+      </x:c>
+      <x:c r="G24" s="56" t="str">
+        <x:v>Open available pickups after accepting a stop</x:v>
+      </x:c>
+      <x:c r="H24" s="56" t="str">
+        <x:v>Available pickup order recalculates based on current route</x:v>
+      </x:c>
+      <x:c r="I24" s="56"/>
+      <x:c r="J24" s="56" t="str">
+        <x:v>Not Run</x:v>
+      </x:c>
+      <x:c r="K24" s="56"/>
+      <x:c r="L24" s="56"/>
     </x:row>
     <x:row r="25">
-      <x:c r="A25" s="22"/>
-      <x:c r="B25" s="22"/>
-      <x:c r="C25" s="22"/>
-      <x:c r="D25" s="22"/>
-      <x:c r="E25" s="22"/>
-      <x:c r="F25" s="22"/>
-      <x:c r="G25" s="22"/>
-      <x:c r="H25" s="22"/>
-      <x:c r="I25" s="22"/>
-      <x:c r="J25" s="22"/>
-      <x:c r="K25" s="22"/>
-      <x:c r="L25" s="22"/>
+      <x:c r="A25" s="56" t="str">
+        <x:v>TC-024</x:v>
+      </x:c>
+      <x:c r="B25" s="56" t="str">
+        <x:v>WG-F071</x:v>
+      </x:c>
+      <x:c r="C25" s="56" t="str">
+        <x:v>Collector Routing</x:v>
+      </x:c>
+      <x:c r="D25" s="56" t="str">
+        <x:v>Collector</x:v>
+      </x:c>
+      <x:c r="E25" s="56" t="str">
+        <x:v>Accept dialog previews route before confirm</x:v>
+      </x:c>
+      <x:c r="F25" s="56" t="str">
+        <x:v>Collector has current stops; pending pickup available</x:v>
+      </x:c>
+      <x:c r="G25" s="56" t="str">
+        <x:v>Click accept but do not confirm</x:v>
+      </x:c>
+      <x:c r="H25" s="56" t="str">
+        <x:v>Dialog shows current stops plus new pickup route preview</x:v>
+      </x:c>
+      <x:c r="I25" s="56"/>
+      <x:c r="J25" s="56" t="str">
+        <x:v>Not Run</x:v>
+      </x:c>
+      <x:c r="K25" s="56"/>
+      <x:c r="L25" s="56"/>
     </x:row>
     <x:row r="26">
-      <x:c r="A26" s="22"/>
-      <x:c r="B26" s="22"/>
-      <x:c r="C26" s="22"/>
-      <x:c r="D26" s="22"/>
-      <x:c r="E26" s="22"/>
-      <x:c r="F26" s="22"/>
-      <x:c r="G26" s="22"/>
-      <x:c r="H26" s="22"/>
-      <x:c r="I26" s="22"/>
-      <x:c r="J26" s="22"/>
-      <x:c r="K26" s="22"/>
-      <x:c r="L26" s="22"/>
+      <x:c r="A26" s="56" t="str">
+        <x:v>TC-025</x:v>
+      </x:c>
+      <x:c r="B26" s="56" t="str">
+        <x:v>WG-F039</x:v>
+      </x:c>
+      <x:c r="C26" s="56" t="str">
+        <x:v>Pickup Lifecycle</x:v>
+      </x:c>
+      <x:c r="D26" s="56" t="str">
+        <x:v>Collector</x:v>
+      </x:c>
+      <x:c r="E26" s="56" t="str">
+        <x:v>Accept pickup action</x:v>
+      </x:c>
+      <x:c r="F26" s="56" t="str">
+        <x:v>Pickup status PENDING</x:v>
+      </x:c>
+      <x:c r="G26" s="56" t="str">
+        <x:v>Collector accepts pickup</x:v>
+      </x:c>
+      <x:c r="H26" s="56" t="str">
+        <x:v>Status changes to ACCEPTED and pickup moves to My Pickups</x:v>
+      </x:c>
+      <x:c r="I26" s="56"/>
+      <x:c r="J26" s="56" t="str">
+        <x:v>Not Run</x:v>
+      </x:c>
+      <x:c r="K26" s="56"/>
+      <x:c r="L26" s="56"/>
     </x:row>
     <x:row r="27">
-      <x:c r="A27" s="22"/>
-      <x:c r="B27" s="22"/>
-      <x:c r="C27" s="22"/>
-      <x:c r="D27" s="22"/>
-      <x:c r="E27" s="22"/>
-      <x:c r="F27" s="22"/>
-      <x:c r="G27" s="22"/>
-      <x:c r="H27" s="22"/>
-      <x:c r="I27" s="22"/>
-      <x:c r="J27" s="22"/>
-      <x:c r="K27" s="22"/>
-      <x:c r="L27" s="22"/>
+      <x:c r="A27" s="56" t="str">
+        <x:v>TC-026</x:v>
+      </x:c>
+      <x:c r="B27" s="56" t="str">
+        <x:v>WG-F040</x:v>
+      </x:c>
+      <x:c r="C27" s="56" t="str">
+        <x:v>Pickup Lifecycle</x:v>
+      </x:c>
+      <x:c r="D27" s="56" t="str">
+        <x:v>Collector</x:v>
+      </x:c>
+      <x:c r="E27" s="56" t="str">
+        <x:v>Arrived pickup action</x:v>
+      </x:c>
+      <x:c r="F27" s="56" t="str">
+        <x:v>Pickup status ACCEPTED</x:v>
+      </x:c>
+      <x:c r="G27" s="56" t="str">
+        <x:v>Collector marks arrived</x:v>
+      </x:c>
+      <x:c r="H27" s="56" t="str">
+        <x:v>Status changes to ARRIVED and customer can no longer cancel</x:v>
+      </x:c>
+      <x:c r="I27" s="56"/>
+      <x:c r="J27" s="56" t="str">
+        <x:v>Not Run</x:v>
+      </x:c>
+      <x:c r="K27" s="56"/>
+      <x:c r="L27" s="56"/>
     </x:row>
     <x:row r="28">
-      <x:c r="A28" s="22"/>
-      <x:c r="B28" s="22"/>
-      <x:c r="C28" s="22"/>
-      <x:c r="D28" s="22"/>
-      <x:c r="E28" s="22"/>
-      <x:c r="F28" s="22"/>
-      <x:c r="G28" s="22"/>
-      <x:c r="H28" s="22"/>
-      <x:c r="I28" s="22"/>
-      <x:c r="J28" s="22"/>
-      <x:c r="K28" s="22"/>
-      <x:c r="L28" s="22"/>
+      <x:c r="A28" s="56" t="str">
+        <x:v>TC-027</x:v>
+      </x:c>
+      <x:c r="B28" s="56" t="str">
+        <x:v>WG-F042</x:v>
+      </x:c>
+      <x:c r="C28" s="56" t="str">
+        <x:v>Pickup Lifecycle</x:v>
+      </x:c>
+      <x:c r="D28" s="56" t="str">
+        <x:v>Collector</x:v>
+      </x:c>
+      <x:c r="E28" s="56" t="str">
+        <x:v>Complete pickup action</x:v>
+      </x:c>
+      <x:c r="F28" s="56" t="str">
+        <x:v>Pickup status VERIFIED</x:v>
+      </x:c>
+      <x:c r="G28" s="56" t="str">
+        <x:v>Collector completes pickup</x:v>
+      </x:c>
+      <x:c r="H28" s="56" t="str">
+        <x:v>Status changes to COMPLETED and rewards/ledger behavior is correct</x:v>
+      </x:c>
+      <x:c r="I28" s="56"/>
+      <x:c r="J28" s="56" t="str">
+        <x:v>Not Run</x:v>
+      </x:c>
+      <x:c r="K28" s="56"/>
+      <x:c r="L28" s="56"/>
     </x:row>
     <x:row r="29">
-      <x:c r="A29" s="22"/>
-      <x:c r="B29" s="22"/>
-      <x:c r="C29" s="22"/>
-      <x:c r="D29" s="22"/>
-      <x:c r="E29" s="22"/>
-      <x:c r="F29" s="22"/>
-      <x:c r="G29" s="22"/>
-      <x:c r="H29" s="22"/>
-      <x:c r="I29" s="22"/>
-      <x:c r="J29" s="22"/>
-      <x:c r="K29" s="22"/>
-      <x:c r="L29" s="22"/>
+      <x:c r="A29" s="56" t="str">
+        <x:v>TC-028</x:v>
+      </x:c>
+      <x:c r="B29" s="56" t="str">
+        <x:v>WG-F074</x:v>
+      </x:c>
+      <x:c r="C29" s="56" t="str">
+        <x:v>Pickup Detail</x:v>
+      </x:c>
+      <x:c r="D29" s="56" t="str">
+        <x:v>Admin/Collector</x:v>
+      </x:c>
+      <x:c r="E29" s="56" t="str">
+        <x:v>Admin and collector slug pages render</x:v>
+      </x:c>
+      <x:c r="F29" s="56" t="str">
+        <x:v>Pickup exists; admin and collector accounts exist</x:v>
+      </x:c>
+      <x:c r="G29" s="56" t="str">
+        <x:v>Open admin and collector pickup slug pages</x:v>
+      </x:c>
+      <x:c r="H29" s="56" t="str">
+        <x:v>Both pages render without guard/resolver errors</x:v>
+      </x:c>
+      <x:c r="I29" s="56"/>
+      <x:c r="J29" s="56" t="str">
+        <x:v>Not Run</x:v>
+      </x:c>
+      <x:c r="K29" s="56"/>
+      <x:c r="L29" s="56"/>
     </x:row>
     <x:row r="30">
-      <x:c r="A30" s="22"/>
-      <x:c r="B30" s="22"/>
-      <x:c r="C30" s="22"/>
-      <x:c r="D30" s="22"/>
-      <x:c r="E30" s="22"/>
-      <x:c r="F30" s="22"/>
-      <x:c r="G30" s="22"/>
-      <x:c r="H30" s="22"/>
-      <x:c r="I30" s="22"/>
-      <x:c r="J30" s="22"/>
-      <x:c r="K30" s="22"/>
-      <x:c r="L30" s="22"/>
+      <x:c r="A30" s="56" t="str">
+        <x:v>TC-029</x:v>
+      </x:c>
+      <x:c r="B30" s="56" t="str">
+        <x:v>WG-F072</x:v>
+      </x:c>
+      <x:c r="C30" s="56" t="str">
+        <x:v>Maps</x:v>
+      </x:c>
+      <x:c r="D30" s="56" t="str">
+        <x:v>Collector</x:v>
+      </x:c>
+      <x:c r="E30" s="56" t="str">
+        <x:v>Route map renders stops without marker drift</x:v>
+      </x:c>
+      <x:c r="F30" s="56" t="str">
+        <x:v>Collector has multiple accepted pickups</x:v>
+      </x:c>
+      <x:c r="G30" s="56" t="str">
+        <x:v>Open My Pickups route map</x:v>
+      </x:c>
+      <x:c r="H30" s="56" t="str">
+        <x:v>MapLibre/OSRM route and stop markers align with actual stop coordinates</x:v>
+      </x:c>
+      <x:c r="I30" s="56"/>
+      <x:c r="J30" s="56" t="str">
+        <x:v>Not Run</x:v>
+      </x:c>
+      <x:c r="K30" s="56"/>
+      <x:c r="L30" s="56"/>
     </x:row>
     <x:row r="31">
       <x:c r="A31" s="22"/>
@@ -11827,12 +12368,12 @@
   </x:conditionalFormatting>
   <x:dataValidations count="1">
     <x:dataValidation type="list" sqref="J2:J200">
-      <x:formula1>Lists!$G$2:$G$5</x:formula1>
+      <x:formula1>"Not Run,Passed,Failed,Blocked"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc218e5cf66e8470d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra478a3463196468e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
